--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0019.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0019.xlsx
@@ -1036,8 +1036,8 @@
         <is>
           <t>Cần bao nhiêu bước để dâng lên lời cầu nguyện thành kính và trang trọng nhất?
 1. Quỳ gối.
-2. Pray.
-3. Stand dậy.</t>
+2. Cầu nguyện.
+3. Đứng dậy.</t>
         </is>
       </c>
     </row>
@@ -1579,10 +1579,10 @@
           <t>Gửi Cô Eri, hay người gửi ẩn danh:
 Hy vọng lá thư này đến tay cô trong an lành.
 Thông tin trong đơn đăng ký cô gửi thuộc về Eri, một thành viên của Hiệp Hội chúng tôi. Đáng tiếc, cô ấy đã mất tích cách đây hàng thập kỷ khi đang thực hiện công tác đánh giá thực địa cho tư cách thành viên tại Honami. Dù cô là Eri hay một người bảo hộ đã hoàn thành công việc của cô ấy, chúng tôi xin gửi lời tri ân sâu sắc. Những gì cô mang về vượt xa giá trị. Nó đã khôi phục một sợi dây liên kết mà chúng tôi tưởng đã đứt lìa mãi mãi.
-Về "Bộ ảnh đặc trưng về Honami City" và đơn đăng ký đã nộp:
+Về "Bộ ảnh đặc trưng về Thành phố Honami" và đơn đăng ký đã nộp:
 Những bức ảnh thể hiện tình yêu sâu sắc của cô dành cho chủ đề. Chúng ghi lại trung thực tinh thần của con người, nền văn minh họ xây dựng và vẻ đẹp độc đáo của quê hương họ. Qua ống kính của cô, chúng tôi không chỉ chứng kiến cuộc sống sôi động của Honami mà còn cảm nhận được ánh sáng rực rỡ, đau thương mà nó để lại cho thế giới khi lụi tàn.
-Sau khi cân nhắc kỹ lưỡng, ban biên tập đã nhất trí thông qua việc xác nhận muộn này. Tác phẩm của cô sẽ được giới thiệu trong một ấn bản đặc biệt tưởng niệm của Wutherium Geographic. Chúng tôi vinh dự chính thức chào đón Eri trở thành thành viên chính thức của Pioneer Association.
-Trụ sở Pioneer Association
+Sau khi cân nhắc kỹ lưỡng, ban biên tập đã nhất trí thông qua việc xác nhận muộn này. Tác phẩm của cô sẽ được giới thiệu trong một ấn bản đặc biệt tưởng niệm của Wutherium Geographic. Chúng tôi vinh dự chính thức chào đón Eri trở thành thành viên chính thức của Hiệp Hội Tiên Phong.
+Trụ sở Hiệp Hội Tiên Phong
 Ban Biên Tập, Wutherium Geographic</t>
         </is>
       </c>
@@ -1862,10 +1862,10 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Ta là Strom, một nhà thám hiểm của Pioneer Association.
+          <t>Ta là Strom, một nhà thám hiểm của Hiệp Hội Tiên Phong.
 Ta đã trải qua mười bốn ngày đêm trong thành phố đang chìm này...
 Nếu có ai đọc được dòng này, ta có một việc cần nhờ...
-Nếu cậu gặp Aria của New Federation, hãy nói với cô ấy...
+Nếu cậu gặp Aria của Liên Bang Mới, hãy nói với cô ấy...
 Aria à, khoảng thời gian bên em... là kho báu quý giá nhất đời ta.
 Cảm ơn em...</t>
         </is>
@@ -2528,7 +2528,7 @@
       <c r="M31" t="inlineStr">
         <is>
           <t>"Khi niềm vui tràn ngập, tiếng cười vang khắp nơi, ngươi sẽ được đáp lại bằng một trận mưa sao nhẹ nhàng."
-Dodget chữ thật phong cách.
+Nét chữ thật phong cách.
 Phong bì mang hương thơm pha trộn giữa nước cam, vỏ chanh và si-rô lựu, một hương vị mà nhiều người trìu mến gọi là "Mưa Sao".</t>
         </is>
       </c>
@@ -2597,7 +2597,7 @@
       <c r="M32" t="inlineStr">
         <is>
           <t>"Khi niềm vui tràn ngập, tiếng cười vang khắp nơi, ngươi sẽ được đáp lại bằng một trận mưa sao nhẹ nhàng."
-Dodget chữ thật phong cách.
+Nét chữ thật phong cách.
 Phong bì mang hương thơm pha trộn giữa nước cam, vỏ chanh và si-rô lựu, một hương vị mà nhiều người trìu mến gọi là "Mưa Sao".</t>
         </is>
       </c>
@@ -3197,17 +3197,17 @@
       <c r="M41" t="inlineStr">
         <is>
           <t>Báo Cáo Đánh Giá Mạch Năng Lực – Cầu Nối và Tĩnh Lực
-Cơ sở đánh giá: Report y tế của Dhalifa
-Tacet Mark của bệnh nhân nằm ở cánh tay phải phía trên. Không xác định được thời điểm chính xác của sự Thức Tỉnh. Khi nhập viện, bệnh nhân tỉnh táo nhưng không giao tiếp. Khi được hỏi về Mạch Năng Lực, cô đã tác động lên một chiếc đồng hồ trong phòng, nâng độ chính xác của nó lên mức femto giây.
+Cơ sở đánh giá: Báo cáo y tế của Dhalifa
+Dấu Tacet của bệnh nhân nằm ở cánh tay phải phía trên. Không xác định được thời điểm chính xác của sự Thức Tỉnh. Khi nhập viện, bệnh nhân tỉnh táo nhưng không giao tiếp. Khi được hỏi về Mạch Năng Lực, cô đã tác động lên một chiếc đồng hồ trong phòng, nâng độ chính xác của nó lên mức femto giây.
 Sau đó, bệnh nhân giải thích qua một robot chăm sóc rằng Mạch Năng Lực của cô có thể ảnh hưởng ngẫu nhiên đến hiệu suất máy móc. Ví dụ, một chiếc đồng hồ khác bị tác động đã chạy chậm lại và không phản hồi khi hiệu chỉnh.
 Do các câu hỏi chỉ nhằm đảm bảo an toàn điều trị, không có kế hoạch điều tra thêm.
-"Một femto giây bằng một phần triệu tỷ giây. Độ chính xác này thật kinh ngạc. Hãy gửi chiếc đồng hồ này đến Startorch Academy. Họ sẽ biết phải làm gì với nó."
+"Một femto giây bằng một phần triệu tỷ giây. Độ chính xác này thật kinh ngạc. Hãy gửi chiếc đồng hồ này đến Học viện Startorch. Họ sẽ biết phải làm gì với nó."
 Kết luận: Mức độ Cộng Hưởng Nguy Hiểm ở mức trung bình. Tình trạng bệnh nhân ổn định ở mức trung bình, nguy cơ Quá Tải thấp.
 Tiền sử Quá Tải đã được ghi nhận.
 Mức độ nghiêm trọng tối đa: Trung bình.
-Bệnh nhân từng Quá Tải trong một cơn Void Storm, hút vật chất Exoswarm vào cơ thể để thay thế mô bị nhiễm độc, giúp cô sống sót. Vật chất tích hợp hiện không phát ra tần số Exoswarm và chỉ hoạt động như mô giả.
+Bệnh nhân từng Quá Tải trong một cơn Bão Hư Không, hút vật chất Exoswarm vào cơ thể để thay thế mô bị nhiễm độc, giúp cô sống sót. Vật chất tích hợp hiện không phát ra tần số Exoswarm và chỉ hoạt động như mô giả.
 Hiện tại, bệnh nhân thể hiện trạng thái cảm xúc ổn định bất thường so với chấn thương và vết thương mà cô phải chịu. Đề xuất đánh giá định kỳ và hỗ trợ tâm lý.
-"Dhalifa chỉ sống sót nhờ Quá Tải. Đây không phải khả năng có thể chống lại Void Storm! Đảm bảo Department Vật Chất Hư Không để cô ấy yên!"</t>
+"Dhalifa chỉ sống sót nhờ Quá Tải. Đây không phải khả năng có thể chống lại Bão Hư Không! Đảm bảo Cục Vật Chất Hư Không để cô ấy yên!"</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Một dải lụa đơn sơ, đơn điệu, thêu tên những người Roya đã mất trong Void Storm tàn phá Spacetrek Observatory. Tên của Dhalifa cũng ở đó, nhưng một sợi chỉ tím đã gạch ngang qua.</t>
+          <t>Một dải lụa đơn sơ, đơn điệu, thêu tên những người Roya đã mất trong Bão Hư Không tàn phá Đài Thiên Văn Spacetrek. Tên của Dhalifa cũng ở đó, nhưng một sợi chỉ tím đã gạch ngang qua.</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
         <is>
           <t>"Vùng đất Lahai-Roi rộng lớn và đầy bí ẩn đã buộc Spacetrek Collective phải thiết lập các chương trình nghiên cứu thực địa trung và dài hạn. Tuy nhiên, để duy trì hoạt động trong địa hình nguy hiểm như vậy, họ cần những căn cứ di động đáng tin cậy.
 Sau khi cân nhắc kỹ lưỡng, Collective đã phát triển một nền tảng vận tải đa năng, có khả năng xử lý hậu cần, lưu trữ và phòng thủ khẩn cấp. Họ đặt tên cho nó là Spacetrek Explorer.
-Thiết kế của Explorer dựa trên một robot bánh xe. Những chiếc lốp khổng lồ giúp nó bám địa hình tốt, cho phép leo lên các bề mặt thẳng đứng trơn nhẵn và dễ dàng di chuyển qua kiến trúc dày đặc của Startorch Academy, vận chuyển hàng hóa đến những nơi khó tiếp cận. Thùng chứa lớn gắn trên đỉnh càng hỗ trợ công tác thực địa, giúp các nhà nghiên cứu tiếp cận vật tư hoặc thiết bị phụ trợ ngay tại chỗ.
+Thiết kế của Explorer dựa trên một robot bánh xe. Những chiếc lốp khổng lồ giúp nó bám địa hình tốt, cho phép leo lên các bề mặt thẳng đứng trơn nhẵn và dễ dàng di chuyển qua kiến trúc dày đặc của Học viện Startorch, vận chuyển hàng hóa đến những nơi khó tiếp cận. Thùng chứa lớn gắn trên đỉnh càng hỗ trợ công tác thực địa, giúp các nhà nghiên cứu tiếp cận vật tư hoặc thiết bị phụ trợ ngay tại chỗ.
 Để chống lại Exoswarm bị ảnh hưởng bởi Hiện tượng Waveworn và các cuộc tấn công từ Outcasts, Explorer được trang bị một khẩu pháo điện từ hạng nặng và máy chiếu lá chắn bảo vệ. Tuy nhiên, do trọng lượng, tải trọng hàng hóa thường xuyên và thiết kế tiết kiệm năng lượng, nó chỉ mang theo các động cơ đẩy nhỏ. Những động cơ này hữu ích cho những đợt tăng tốc ngắn, nhưng không thể bay liên tục.
 Ngoài các chuyến thám hiểm thực địa, Spacetrek Explorer hiện còn đóng vai trò là một trong những phương tiện hậu cần hạng nặng chủ lực của Lahai-Roi. Ở cấu hình hậu cần, vũ khí của nó được tháo bỏ và thay thế bằng các mô-đun lưu trữ mở rộng để tối đa hóa sức chứa hàng hóa."</t>
         </is>
@@ -3567,8 +3567,8 @@
       <c r="M46" t="inlineStr">
         <is>
           <t>"Các Điều phối viên phải tuân thủ nghiêm ngặt các bước dưới đây để vận hành Bộ Xây Dựng Tuyến Đường.
-Bước 1: Đặt lượng Compressed Bedrock cần thiết vào.
-Lưu ý: Compressed Bedrock là vật liệu đã qua xử lý, được tạo thành từ khoáng chất tự nhiên. Sau khi tinh chế đá Lahai-Roi nguyên sinh, Tập đoàn Spacetrek sản xuất ra một loại vật liệu xây dựng có mật độ cao. Sau khi được Bộ Xây Dựng Tuyến Đường phân tích và tách chiết, nó có thể kết hợp với các tài nguyên khác để tạo thành các tấm nền cấu trúc cho nhiều loại công trình.
+Bước 1: Đặt lượng Đá Nền Nén cần thiết vào.
+Lưu ý: Đá Nền Nén là vật liệu đã qua xử lý, được tạo thành từ khoáng chất tự nhiên. Sau khi tinh chế đá Lahai-Roi nguyên sinh, Tập đoàn Spacetrek sản xuất ra một loại vật liệu xây dựng có mật độ cao. Sau khi được Bộ Xây Dựng Tuyến Đường phân tích và tách chiết, nó có thể kết hợp với các tài nguyên khác để tạo thành các tấm nền cấu trúc cho nhiều loại công trình.
 Bước 2: Đặt lượng Mechanite cần thiết vào.
 Lưu ý: Mechanite là một loại khoáng chất bản địa của Lahai-Roi. Sau khi Exostrider xuất hiện, các cấu trúc và hoa văn cơ khí bắt đầu phát triển trên nó dưới ảnh hưởng của chúng. Tập đoàn phát hiện ra rằng các thiết bị điện tử được chế tạo từ khoáng chất này có hiệu suất tính toán tăng cao, như thể chính Mechanite có khả năng xử lý.
 Bước 3: Đặt lượng Lõi Bộ Xây Dựng cần thiết vào.
@@ -3653,7 +3653,7 @@
 - Pathfinder: Phương tiện cỡ trung dùng để vận chuyển nhân sự, có khả năng chở hàng hạn chế.
 - Sprinter: Phương tiện nhỏ tối ưu cho di chuyển nhanh và đơn độc.
 Do số lượng phương tiện có hạn, tất cả các đơn đăng ký đều phải nộp đơn yêu cầu chính thức. Nhân viên sẽ xem xét từng đơn và phân bổ phương tiện dựa trên nhu cầu thực tế.
-'Gần đây, dường như tất cả Hauler ở Lahai-Roi đều đổ về Spacetrek Observatory. Dự án đó lớn đến mức nào vậy?'"</t>
+'Gần đây, dường như tất cả Hauler ở Lahai-Roi đều đổ về Đài Quan Sát Spacetrek. Dự án đó lớn đến mức nào vậy?'"</t>
         </is>
       </c>
     </row>
@@ -3721,10 +3721,10 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>"Spacetrek Observatory là một công trình vĩ đại do Spacetrek Collective và Roya cùng xây dựng. Nhiệm vụ của nó là lập bản đồ các điểm dữ liệu khác nhau của Lahai-Roi. Khác với Cassette lưu trữ dữ liệu cá nhân, Đài Thiên Văn chủ yếu ghi lại và theo dõi những biến đổi về địa hình, hệ sinh thái, khí hậu và bầu trời của Lahai-Roi dưới ảnh hưởng của Void Storm và hoạt động của Threnodian.
-Khi mối quan hệ hợp tác với Roya ngày càng sâu sắc, Đài Thiên Văn còn bắt đầu ghi chép lại kiến trúc và các địa danh văn hóa của họ. Nhưng rồi thảm họa ập đến. Một cơn Void Storm khủng khiếp quét qua, phá hủy toàn bộ công trình. Dù Học Viện đã bắt đầu tái thiết, tiến độ lại vô cùng chậm chạp. Số lượng dự án đang triển khai khắp Lahai-Roi quá lớn, cộng với những con đường dẫn đến địa điểm bị hư hại, khiến công trình đồ sộ này rơi vào cảnh hoang tàn.
-Đó là phần giới thiệu về Spacetrek Observatory. Ta tin rằng giờ đây các ngươi đã hiểu được tầm quan trọng của nó. Dù hiện tại còn nhiều khó khăn, việc khôi phục nó là điều cần thiết! Đó là lý do ta kêu gọi từng người trong các ngươi cùng tham gia vào sứ mệnh quan trọng này. Chúng ta cần sự giúp đỡ của các ngươi, dưới bất kỳ hình thức nào. Mọi đóng góp đều có ý nghĩa.
-Ta là Rakosan. Ta sẽ ở đây, tại Spacetrek Observatory, chờ đợi các ngươi!"</t>
+          <t>"Đài Thiên Văn Spacetrek là một công trình vĩ đại do Tập Đoàn Spacetrek và Roya cùng xây dựng. Nhiệm vụ của nó là lập bản đồ các điểm dữ liệu khác nhau của Lahai-Roi. Khác với Cassette lưu trữ dữ liệu cá nhân, Đài Thiên Văn chủ yếu ghi lại và theo dõi những biến đổi về địa hình, hệ sinh thái, khí hậu và bầu trời của Lahai-Roi dưới ảnh hưởng của Bão Hư Không và hoạt động của Threnodian.
+Khi mối quan hệ hợp tác với Roya ngày càng sâu sắc, Đài Thiên Văn còn bắt đầu ghi chép lại kiến trúc và các địa danh văn hóa của họ. Nhưng rồi thảm họa ập đến. Một cơn Bão Hư Không khủng khiếp quét qua, phá hủy toàn bộ công trình. Dù Học Viện đã bắt đầu tái thiết, tiến độ lại vô cùng chậm chạp. Số lượng dự án đang triển khai khắp Lahai-Roi quá lớn, cộng với những con đường dẫn đến địa điểm bị hư hại, khiến công trình đồ sộ này rơi vào cảnh hoang tàn.
+Đó là phần giới thiệu về Đài Thiên Văn Spacetrek. Ta tin rằng giờ đây các ngươi đã hiểu được tầm quan trọng của nó. Dù hiện tại còn nhiều khó khăn, việc khôi phục nó là điều cần thiết! Đó là lý do ta kêu gọi từng người trong các ngươi cùng tham gia vào sứ mệnh quan trọng này. Chúng ta cần sự giúp đỡ của các ngươi, dưới bất kỳ hình thức nào. Mọi đóng góp đều có ý nghĩa.
+Ta là Rakosan. Ta sẽ ở đây, tại Đài Thiên Văn Spacetrek, chờ đợi các ngươi!"</t>
         </is>
       </c>
     </row>
@@ -4654,8 +4654,8 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Cột Teacher, Số 5:
-"Thời trang là cách thể hiện bản thân, là tấm gương phản chiếu con người và tâm hồn ta. Sự khác biệt về kích cỡ, sự cân đối hay bất đối xứng, những đường Dodget cong hay thẳng… tất cả đều âm thầm định hình cách ta nhìn nhận chính mình và cách thế giới nhìn ta. Styling, về bản chất, là một thử nghiệm tinh tế và duyên dáng, là cách người thiết kế diễn giải thế giới và cảnh sắc luôn biến đổi qua lăng kính của riêng họ."
+          <t>Cột Thầy, Số 5:
+"Thời trang là cách thể hiện bản thân, là tấm gương phản chiếu con người và tâm hồn ta. Sự khác biệt về kích cỡ, sự cân đối hay bất đối xứng, những đường nét cong hay thẳng… tất cả đều âm thầm định hình cách ta nhìn nhận chính mình và cách thế giới nhìn ta. Styling, về bản chất, là một thử nghiệm tinh tế và duyên dáng, là cách người thiết kế diễn giải thế giới và cảnh sắc luôn biến đổi qua lăng kính của riêng họ."
 "Ánh nắng ấm áp tràn ngập khuôn viên. Một chiếc áo len cổ lọ màu xám, vai trễ, kết hợp với chân váy kẻ caro cổ điển, cùng chiếc túi xách tone tối vừa vặn. Chiếc trâm bướm vàng óng ánh nhẹ nhàng trên ngực, mang đến chút duyên dáng cho sắc xám trầm lặng. Một chút hoài cổ hòa quyện hoàn hảo với không khí học thuật hiện đại, như thể thời gian đã chậm lại..."</t>
         </is>
       </c>
@@ -4794,8 +4794,8 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Name: Sevi
-Gender: Male
+          <t>Tên: Sevi
+Giới tính: Nam
 Tuổi: 35
 Giáo sư Sevi đã được trao tặng Huân chương Startorch vì Thành tựu Khoa học để ghi nhận những đóng góp học thuật của ông.
 Những cống hiến của ông cho cộng đồng khoa học bao gồm thiết kế và cải tiến các dụng cụ đo lường chính xác, cũng như nhiều thiết bị kỹ thuật khác.</t>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Tích năng lượng và nhận Shield trong lúc triệu hồi một cơn bão khổng lồ, giải phóng lốc xoáy tấn công tứ phía. Phá vỡ Shield sẽ làm gián đoạn quá trình tích năng và khiến nó bị bất động.</t>
+          <t>Tích năng lượng và nhận Khiên trong lúc triệu hồi một cơn bão khổng lồ, giải phóng lốc xoáy tấn công tứ phía. Phá vỡ Khiên sẽ làm gián đoạn quá trình tích năng và khiến nó bị bất động.</t>
         </is>
       </c>
     </row>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Tích năng lượng và nhận Shield trong lúc triệu hồi liên tiếp 4 ma trận phía sau. Các ma trận sẽ bắn tia laser về phía trước khi được triệu hồi xong. Phá vỡ Shield sẽ làm gián đoạn quá trình tích năng và khiến nó bị bất động.</t>
+          <t>Tích năng lượng và nhận Khiên trong lúc triệu hồi liên tiếp 4 ma trận phía sau. Các ma trận sẽ bắn tia laser về phía trước khi được triệu hồi xong. Phá vỡ Khiên sẽ làm gián đoạn quá trình tích năng và khiến nó bị bất động.</t>
         </is>
       </c>
     </row>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Tích năng lượng và nhận Shield trong lúc triệu hồi liên tiếp 5 ngọn giáo phía sau. Khi triệu hồi xong, phóng 5 ngọn giáo tấn công. Phá vỡ Shield sẽ làm gián đoạn quá trình tích năng và khiến nó bị bất động.</t>
+          <t>Tích năng lượng và nhận Khiên trong lúc triệu hồi liên tiếp 5 ngọn giáo phía sau. Khi triệu hồi xong, phóng 5 ngọn giáo tấn công. Phá vỡ Khiên sẽ làm gián đoạn quá trình tích năng và khiến nó bị bất động.</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Tích trữ năng lượng và nhận Shield, đồng thời liên tục phun khói dày đặc và tấn công bằng lửa trong phạm vi rộng. Phá vỡ Shield sẽ làm gián đoạn quá trình tích trữ và khiến nó bị bất động.</t>
+          <t>Tích trữ năng lượng và nhận Khiên, đồng thời liên tục phun khói dày đặc và tấn công bằng lửa trong phạm vi rộng. Phá vỡ Khiên sẽ làm gián đoạn quá trình tích trữ và khiến nó bị bất động.</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Với linh vật gấp giấy của mình, Hiyuki thăm dò sâu trong Voidspace và phát hiện tần số còn vương vấn của Aemeath. Khi Vật Chất Hư Vô ngày càng bất ổn, Lucilla định giao cho Hiyuki nhiệm vụ trông coi Dimmr Plains. Nhưng trước đó, Hiyuki vẫn còn vài chuyện chưa giải quyết xong...</t>
+          <t>Với linh vật gấp giấy của mình, Hiyuki thăm dò sâu trong Không Gian Hư Vô và phát hiện tần số còn vương vấn của Aemeath. Khi Vật Chất Hư Vô ngày càng bất ổn, Lucilla định giao cho Hiyuki nhiệm vụ trông coi Đồng Bằng Dimmr. Nhưng trước đó, Hiyuki vẫn còn vài chuyện chưa giải quyết xong...</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Sau trận chiến quyết định, Spacetrek Collective và Startorch Academy dần trở lại hoạt động bình thường.
+          <t>Sau trận chiến quyết định, Spacetrek Collective và Học viện Startorch dần trở lại hoạt động bình thường.
 Vài ngày sau sự kiện, cậu nghe được tin tức về Denia từ Spacetrek Collective...</t>
         </is>
       </c>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Gửi những Rover đã đồng hành cùng chúng ta trên chặng đường dài, ta cảm ơn các ngươi đã có mặt ở đây. Trong sự kiện, hãy mở khóa và nhận thưởng từ sự kiện Quà Tặng Đại Kỷ Niệm.</t>
+          <t>Gửi những Vận Mệnh Giả đã đồng hành cùng chúng ta trên chặng đường dài, ta cảm ơn các ngươi đã có mặt ở đây. Trong sự kiện, hãy mở khóa và nhận thưởng từ sự kiện Quà Tặng Đại Kỷ Niệm.</t>
         </is>
       </c>
     </row>
@@ -9281,7 +9281,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Những bài test tiêu chuẩn khiến cậu chán ngấy, nhưng một bài test kỹ năng chiến đấu lại khiến máu cậu sôi sục. Vậy thì hãy dốc hết sức và bước vào cuộc đọ sức giành vị trí Huấn Luyện Viên của Bài Kiểm Tra Kỹ Năng Combat B.1.N.G.O.!</t>
+          <t>Những bài kiểm tra tiêu chuẩn khiến cậu chán ngấy, nhưng một bài kiểm tra kỹ năng chiến đấu lại khiến máu cậu sôi sục. Vậy thì hãy dốc hết sức và bước vào cuộc đọ sức giành vị trí Huấn Luyện Viên của Bài Kiểm Tra Kỹ Năng Chiến Đấu B.1.N.G.O.!</t>
         </is>
       </c>
     </row>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Lollo Logistics một lần nữa hợp tác với Pioneer Association hân hạnh giới thiệu chiến dịch phong phú: Beyond the Waves! Upload Nhật Ký Phiêu Lưu nhận được sau khi hoàn thành nhiệm vụ hằng ngày, và nhận "Gói Phiêu Lưu" tương ứng với địa điểm đó, chứa đầy bất ngờ!</t>
+          <t>Lollo Logistics một lần nữa hợp tác với Hiệp Hội Tiên Phong hân hạnh giới thiệu chiến dịch phong phú: Beyond the Waves! Tải lên Nhật Ký Phiêu Lưu nhận được sau khi hoàn thành nhiệm vụ hằng ngày, và nhận "Gói Phiêu Lưu" tương ứng với địa điểm đó, chứa đầy bất ngờ!</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Invite lại những Resonator cũ và hoàn thành nhiệm vụ cùng nhau để nhận Astrites, Shell Credits và nhiều phần thưởng khác! Các Rover quay lại liên kết tài khoản sẽ nhận thêm quà tặng đặc biệt!</t>
+          <t>Mời lại những Cộng Hưởng Giả cũ và hoàn thành nhiệm vụ cùng nhau để nhận Astrites, Shell Credits và nhiều phần thưởng khác! Các Vận Mệnh Giả quay lại liên kết tài khoản sẽ nhận thêm quà tặng đặc biệt!</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Lễ kỷ niệm 2 năm Second Coming of Solaris chính thức khởi động! Năm nay, sự kiện được đồng tổ chức bởi bốn đối tác: Spacetrek Collective, Startorch Academy, Lollo Logistics và Pioneer Association. Hãy tham gia và nhận về kho phần thưởng hấp dẫn!</t>
+          <t>Lễ kỷ niệm 2 năm Sự Trở Lại Của Solaris chính thức khởi động! Năm nay, sự kiện được đồng tổ chức bởi bốn đối tác: Spacetrek Collective, Học viện Startorch, Lollo Logistics và Hiệp hội Pioneer. Hãy tham gia và nhận về kho phần thưởng hấp dẫn!</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Plush Dream Gòn
+          <t>Giấc Mộng Bông Gòn
 Bộ trang phục cao cấp Mornye
 Ngoài khung cửa sổ, tuyết rơi muộn vào đầu xuân. Trong khoảng lặng chờ đợi ấy, cô bé chìm vào một giấc mơ dịu dàng.
 Nơi đó, cô thấy một bầu trời sao xa xăm, hơi ấm trong lòng bàn tay, và người cô hằng đợi chờ, đã đến đúng như lời hứa.</t>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Từ 30/04/2026 đến 21/05/2026, cậu có thể nhận được Livery hợp tác "Kaiju Không. 8" bằng cách hoàn thành các nhiệm vụ chỉ định.
+          <t>Từ 30/04/2026 đến 21/05/2026, cậu có thể nhận được Livery hợp tác "Kaiju No. 8" bằng cách hoàn thành các nhiệm vụ chỉ định.
 *Chỉ để hiển thị. Không xếp theo thứ tự cụ thể.</t>
         </is>
       </c>
@@ -10282,7 +10282,7 @@
       <c r="M146" t="inlineStr">
         <is>
           <t>ROM độc quyền của Zhezhi.
-Con dấu của người nghệ sĩ được trang trí bằng những mầm non phủ sương giá. Nó được đóng lên vô số bức tranh vẽ núi non và hẻm vực bằng những Dodget cọ biểu cảm, mê hoặc. Những mầm non ấy tượng trưng cho sự nở rộ bất tận của những tuyệt tác nghệ thuật.</t>
+Con dấu của người nghệ sĩ được trang trí bằng những mầm non phủ sương giá. Nó được đóng lên vô số bức tranh vẽ núi non và hẻm vực bằng những nét cọ biểu cảm, mê hoặc. Những mầm non ấy tượng trưng cho sự nở rộ bất tận của những tuyệt tác nghệ thuật.</t>
         </is>
       </c>
     </row>
